--- a/data/trans_orig/Q45B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q45B-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2007</t>
+          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16860</t>
+          <t>17537</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25769</t>
+          <t>26379</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15932</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36985</t>
+          <t>39122</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>252383</t>
+          <t>251996</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>267772</t>
+          <t>266981</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>230229</t>
+          <t>231371</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>248575</t>
+          <t>248342</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>490605</t>
+          <t>488704</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>513430</t>
+          <t>513135</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>957</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>12751</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21615</t>
+          <t>20749</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43106</t>
+          <t>42216</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>26448</t>
+          <t>26485</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50425</t>
+          <t>50393</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>477389</t>
+          <t>477202</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>488607</t>
+          <t>488553</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>458980</t>
+          <t>459446</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>480726</t>
+          <t>481651</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>941171</t>
+          <t>942224</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>967222</t>
+          <t>967414</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -1644,97 +1644,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6014</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5010</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>5058</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>4978</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37825</t>
+          <t>38510</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40286</t>
+          <t>39816</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>311562</t>
+          <t>312022</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>296330</t>
+          <t>295716</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>316510</t>
+          <t>317232</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>612511</t>
+          <t>613870</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>634594</t>
+          <t>633618</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8883</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11948</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18389</t>
+          <t>18584</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38958</t>
+          <t>37990</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22367</t>
+          <t>23073</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44089</t>
+          <t>44605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>343995</t>
+          <t>344299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>355944</t>
+          <t>356158</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>331618</t>
+          <t>332774</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>352435</t>
+          <t>352513</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>682302</t>
+          <t>682687</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>705398</t>
+          <t>705171</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -2556,97 +2556,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1885</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25040</t>
+          <t>25841</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30568</t>
+          <t>32183</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>192212</t>
+          <t>191894</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201566</t>
+          <t>201592</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>182628</t>
+          <t>181827</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>198443</t>
+          <t>198677</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>380408</t>
+          <t>378793</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>398507</t>
+          <t>398333</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -3012,97 +3012,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5172</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>1028</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>5125</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>5608</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1028</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>5169</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23321</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43613</t>
+          <t>43557</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23050</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45317</t>
+          <t>45895</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>267223</t>
+          <t>266029</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>232683</t>
+          <t>233359</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>253789</t>
+          <t>253803</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>502508</t>
+          <t>501782</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>525705</t>
+          <t>525507</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,47 +3503,47 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>992</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>11328</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>44932</t>
+          <t>44593</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>72196</t>
+          <t>74098</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>47262</t>
+          <t>46992</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>78864</t>
+          <t>77855</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>603830</t>
+          <t>603719</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>613298</t>
+          <t>614022</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>566023</t>
+          <t>564121</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>593287</t>
+          <t>593626</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1173392</t>
+          <t>1175013</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1205130</t>
+          <t>1205647</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10472</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>15443</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>34992</t>
+          <t>34087</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>31717</t>
+          <t>32232</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>58241</t>
+          <t>57749</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>53028</t>
+          <t>54142</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>86425</t>
+          <t>84877</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>705201</t>
+          <t>705267</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>726221</t>
+          <t>725604</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>720352</t>
+          <t>720074</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>747314</t>
+          <t>746712</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1431540</t>
+          <t>1434014</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1467254</t>
+          <t>1465769</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>14369</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>33890</t>
+          <t>35520</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>41981</t>
+          <t>40685</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>72690</t>
+          <t>71108</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>221465</t>
+          <t>222005</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>282271</t>
+          <t>284702</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>272474</t>
+          <t>274280</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>342837</t>
+          <t>343549</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3193555</t>
+          <t>3192980</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3227215</t>
+          <t>3226611</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3083760</t>
+          <t>3080756</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3145380</t>
+          <t>3144442</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6287720</t>
+          <t>6287354</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6363238</t>
+          <t>6360052</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2012</t>
+          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13934</t>
+          <t>14796</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>880</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9052</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25902</t>
+          <t>25070</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11533</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28553</t>
+          <t>29699</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>287036</t>
+          <t>286118</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>293901</t>
+          <t>293858</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>254838</t>
+          <t>253081</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>273387</t>
+          <t>272825</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>544773</t>
+          <t>544545</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>565516</t>
+          <t>566067</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13067</t>
+          <t>13365</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23113</t>
+          <t>22902</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30212</t>
+          <t>29756</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>492460</t>
+          <t>492162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>502675</t>
+          <t>502696</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>494708</t>
+          <t>495111</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>512545</t>
+          <t>512837</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>993612</t>
+          <t>992454</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1012762</t>
+          <t>1012681</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>991</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12765</t>
+          <t>12847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29642</t>
+          <t>31007</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33992</t>
+          <t>33548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315391</t>
+          <t>315371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322185</t>
+          <t>322181</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>306133</t>
+          <t>305159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>324616</t>
+          <t>325115</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>625544</t>
+          <t>625857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>645457</t>
+          <t>645402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>21806</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22064</t>
+          <t>22140</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>367478</t>
+          <t>368030</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>365000</t>
+          <t>364979</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>379246</t>
+          <t>379219</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>735997</t>
+          <t>735435</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>751056</t>
+          <t>751314</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,62 +6931,62 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1134</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5577</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1134</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>6020</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>13336</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>203580</t>
+          <t>204581</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>206775</t>
+          <t>207012</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>215932</t>
+          <t>216653</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>415338</t>
+          <t>414956</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>426283</t>
+          <t>426112</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>12545</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14069</t>
+          <t>13602</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>10834</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19589</t>
+          <t>18966</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>27187</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>260285</t>
+          <t>261081</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>270922</t>
+          <t>270854</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>250457</t>
+          <t>251417</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>268473</t>
+          <t>267591</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>516673</t>
+          <t>516326</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>536672</t>
+          <t>535727</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8920</t>
+          <t>9817</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>11810</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26169</t>
+          <t>25820</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>44563</t>
+          <t>45823</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>74550</t>
+          <t>76535</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>56338</t>
+          <t>56441</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>93875</t>
+          <t>91206</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>628751</t>
+          <t>629397</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>647926</t>
+          <t>647770</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>613020</t>
+          <t>611765</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>643766</t>
+          <t>642312</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1248169</t>
+          <t>1250454</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1286053</t>
+          <t>1286774</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>18774</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22186</t>
+          <t>20752</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>32733</t>
+          <t>33824</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>61315</t>
+          <t>61119</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>72814</t>
+          <t>72531</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>110056</t>
+          <t>108375</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>113027</t>
+          <t>110556</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>159612</t>
+          <t>158530</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>713710</t>
+          <t>714258</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>743383</t>
+          <t>742410</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>698682</t>
+          <t>700127</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>737709</t>
+          <t>736419</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1424534</t>
+          <t>1424911</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1472905</t>
+          <t>1474797</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,38%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>14022</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>22600</t>
+          <t>23368</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>45214</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>28391</t>
+          <t>28197</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>56160</t>
+          <t>56159</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>60775</t>
+          <t>61465</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>98094</t>
+          <t>100013</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>199460</t>
+          <t>200194</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>263049</t>
+          <t>260980</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>275538</t>
+          <t>274911</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>342120</t>
+          <t>345805</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3307100</t>
+          <t>3306381</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3345692</t>
+          <t>3346047</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3246987</t>
+          <t>3248968</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3313750</t>
+          <t>3313699</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6569184</t>
+          <t>6570313</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6643390</t>
+          <t>6646195</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2016</t>
+          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9412,82 +9412,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2103</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4675</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>922</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5126</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17192</t>
+          <t>15839</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21619</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>278687</t>
+          <t>277948</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>287444</t>
+          <t>287429</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>270563</t>
+          <t>271686</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>284774</t>
+          <t>284396</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>555361</t>
+          <t>555335</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>570462</t>
+          <t>570492</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9868,97 +9868,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2071</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2052</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>979</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>498410</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>500437</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>514668</t>
+          <t>514587</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>522104</t>
+          <t>522110</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1014541</t>
+          <t>1014413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1022541</t>
+          <t>1022542</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -10324,97 +10324,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1820</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>1707</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5989</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1707</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>5368</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12582</t>
+          <t>12464</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27761</t>
+          <t>29016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13988</t>
+          <t>13475</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31469</t>
+          <t>30073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>311806</t>
+          <t>312264</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>302355</t>
+          <t>301033</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>318727</t>
+          <t>318448</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>616417</t>
+          <t>618063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>634764</t>
+          <t>635278</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14358</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15899</t>
+          <t>15231</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>362082</t>
+          <t>361314</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>369234</t>
+          <t>369124</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>381637</t>
+          <t>381595</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>734684</t>
+          <t>735315</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>748701</t>
+          <t>747888</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -11236,97 +11236,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1903</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1874</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>826</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>203183</t>
+          <t>203698</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>210340</t>
+          <t>210327</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11477,7 +11477,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>210041</t>
+          <t>210941</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>216939</t>
+          <t>216934</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>418193</t>
+          <t>417093</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>427176</t>
+          <t>427121</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -11692,97 +11692,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>878</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>12213</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>255278</t>
+          <t>255321</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>262180</t>
+          <t>262176</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>263975</t>
+          <t>264847</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>271217</t>
+          <t>271225</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>523256</t>
+          <t>523013</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>532624</t>
+          <t>533313</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>921</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8691</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>930</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12985</t>
+          <t>13486</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>26342</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>34532</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>639271</t>
+          <t>638770</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>650059</t>
+          <t>650074</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>656546</t>
+          <t>656736</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>674317</t>
+          <t>674705</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1301018</t>
+          <t>1299412</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1321729</t>
+          <t>1321184</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -12609,7 +12609,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5971</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>19559</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>20439</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>19671</t>
+          <t>18656</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>33253</t>
+          <t>34161</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>58644</t>
+          <t>61424</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>44174</t>
+          <t>43610</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>74079</t>
+          <t>72741</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>756977</t>
+          <t>757889</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>770841</t>
+          <t>771004</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>753630</t>
+          <t>751568</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>781456</t>
+          <t>781886</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1515930</t>
+          <t>1515475</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1549182</t>
+          <t>1548175</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>13252</t>
+          <t>12947</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>31120</t>
+          <t>30863</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>44154</t>
+          <t>43054</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>87569</t>
+          <t>87907</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>126045</t>
+          <t>126287</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>113955</t>
+          <t>115839</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>158730</t>
+          <t>161425</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3333318</t>
+          <t>3334937</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3358024</t>
+          <t>3357023</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3386030</t>
+          <t>3384644</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3427890</t>
+          <t>3426550</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6728692</t>
+          <t>6729097</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6778469</t>
+          <t>6776837</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q45B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q45B-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>16485</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26379</t>
+          <t>25546</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16986</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39122</t>
+          <t>35795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>251996</t>
+          <t>252572</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>266981</t>
+          <t>267830</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>231371</t>
+          <t>230830</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>248342</t>
+          <t>248312</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>488704</t>
+          <t>491436</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>513135</t>
+          <t>512339</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>937</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8770</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20749</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42216</t>
+          <t>41039</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>26485</t>
+          <t>26334</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50393</t>
+          <t>51508</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>477202</t>
+          <t>477016</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>488553</t>
+          <t>489055</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>459446</t>
+          <t>459605</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>481651</t>
+          <t>481249</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>942224</t>
+          <t>940971</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>967414</t>
+          <t>967579</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17722</t>
+          <t>18063</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38510</t>
+          <t>38980</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19869</t>
+          <t>20086</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39816</t>
+          <t>41185</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>312022</t>
+          <t>313112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>295716</t>
+          <t>294414</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>317232</t>
+          <t>316369</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>613870</t>
+          <t>612380</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>633618</t>
+          <t>633466</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7599</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18584</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37990</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>21993</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44605</t>
+          <t>44201</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>344299</t>
+          <t>344386</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>356158</t>
+          <t>355713</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>332774</t>
+          <t>332100</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>352513</t>
+          <t>352352</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>682687</t>
+          <t>681780</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>705171</t>
+          <t>705711</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>11887</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25841</t>
+          <t>26116</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>32183</t>
+          <t>32602</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>191894</t>
+          <t>191421</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201592</t>
+          <t>201522</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>181827</t>
+          <t>181552</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>198677</t>
+          <t>198535</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>378793</t>
+          <t>378374</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>398333</t>
+          <t>397655</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22497</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43557</t>
+          <t>44235</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22314</t>
+          <t>22911</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45895</t>
+          <t>46794</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>266029</t>
+          <t>267227</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>233359</t>
+          <t>232133</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>253803</t>
+          <t>254547</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>501782</t>
+          <t>500803</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>525507</t>
+          <t>525292</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11328</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>44593</t>
+          <t>43515</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>74098</t>
+          <t>71462</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46992</t>
+          <t>47571</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>77855</t>
+          <t>79236</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>603719</t>
+          <t>603584</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>614022</t>
+          <t>613330</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>564121</t>
+          <t>566757</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>593626</t>
+          <t>594704</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1175013</t>
+          <t>1173097</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1205647</t>
+          <t>1204702</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>849</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10472</t>
+          <t>10257</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>16555</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>15443</t>
+          <t>15176</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>34087</t>
+          <t>34227</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>32232</t>
+          <t>32562</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>57749</t>
+          <t>59064</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>54142</t>
+          <t>52692</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>84877</t>
+          <t>84224</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>705267</t>
+          <t>705220</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>725604</t>
+          <t>726234</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>720074</t>
+          <t>719465</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>746712</t>
+          <t>746959</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1434014</t>
+          <t>1434383</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1465769</t>
+          <t>1467122</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20592</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>14772</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>35532</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>40685</t>
+          <t>41649</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>71108</t>
+          <t>70841</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>222005</t>
+          <t>223995</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>284702</t>
+          <t>286479</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>274280</t>
+          <t>270478</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>343549</t>
+          <t>336891</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3192980</t>
+          <t>3194420</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3226611</t>
+          <t>3226769</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3080756</t>
+          <t>3079454</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3144442</t>
+          <t>3144532</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6287354</t>
+          <t>6294006</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6360052</t>
+          <t>6363882</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14464</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14796</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>871</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25070</t>
+          <t>25856</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>12174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29699</t>
+          <t>29565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>286118</t>
+          <t>286487</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>293858</t>
+          <t>293867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>253081</t>
+          <t>252837</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>272825</t>
+          <t>273958</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>544545</t>
+          <t>543156</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>566067</t>
+          <t>565153</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9291</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13365</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22902</t>
+          <t>21143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11913</t>
+          <t>11902</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29756</t>
+          <t>29449</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>492162</t>
+          <t>491926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>502696</t>
+          <t>502686</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>495111</t>
+          <t>495580</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>512837</t>
+          <t>512678</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>992454</t>
+          <t>994721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1012681</t>
+          <t>1013379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>995</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9189</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>13496</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>30953</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>14838</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33548</t>
+          <t>32926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315371</t>
+          <t>314297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322181</t>
+          <t>322182</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>305159</t>
+          <t>305671</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>325115</t>
+          <t>324500</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>625857</t>
+          <t>626410</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>645402</t>
+          <t>645111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21806</t>
+          <t>21820</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22140</t>
+          <t>22048</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>368030</t>
+          <t>367561</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>364979</t>
+          <t>365349</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>379219</t>
+          <t>379314</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>735435</t>
+          <t>736037</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>751314</t>
+          <t>751052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11635</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>13787</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>204581</t>
+          <t>204526</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>207012</t>
+          <t>207013</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>216653</t>
+          <t>216664</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>414956</t>
+          <t>414701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>426112</t>
+          <t>426333</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13050</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>9757</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27187</t>
+          <t>26294</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>261081</t>
+          <t>261053</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>270854</t>
+          <t>270860</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>251417</t>
+          <t>250952</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>267591</t>
+          <t>267856</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>516326</t>
+          <t>516237</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>535727</t>
+          <t>535843</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9817</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,47 +7858,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>4887</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>1854</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>10790</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>4887</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>1939</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>11810</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25820</t>
+          <t>25036</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>45823</t>
+          <t>46779</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>76535</t>
+          <t>76623</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>56441</t>
+          <t>58555</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>91206</t>
+          <t>92640</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>629397</t>
+          <t>629381</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>647770</t>
+          <t>647710</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>611765</t>
+          <t>610101</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>642312</t>
+          <t>642306</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1250454</t>
+          <t>1249977</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1286774</t>
+          <t>1284744</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>18189</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>20752</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>33824</t>
+          <t>32818</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>61119</t>
+          <t>59752</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>72531</t>
+          <t>74068</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>108375</t>
+          <t>109581</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>110556</t>
+          <t>115497</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>158530</t>
+          <t>162658</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>714258</t>
+          <t>715691</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>742410</t>
+          <t>742939</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>700127</t>
+          <t>698218</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>736419</t>
+          <t>737037</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1424911</t>
+          <t>1421290</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1474797</t>
+          <t>1469625</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,05%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>15788</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,82 +8735,82 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>32967</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>22554</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>45786</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>40183</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>28695</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>55071</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>32967</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>23368</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>45214</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>40183</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>28197</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>56159</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>61465</t>
+          <t>61565</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>100013</t>
+          <t>96528</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>200194</t>
+          <t>200743</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>260980</t>
+          <t>262413</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>274911</t>
+          <t>274648</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>345805</t>
+          <t>346383</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3306381</t>
+          <t>3307123</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3346047</t>
+          <t>3343884</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3248968</t>
+          <t>3249607</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3313699</t>
+          <t>3312732</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6570313</t>
+          <t>6570169</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6646195</t>
+          <t>6644153</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>22414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>277948</t>
+          <t>278642</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>287429</t>
+          <t>287419</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>271686</t>
+          <t>270584</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>284396</t>
+          <t>284361</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>555335</t>
+          <t>554543</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>570492</t>
+          <t>570585</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8497</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>8385</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>514587</t>
+          <t>514578</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>522110</t>
+          <t>522106</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1014413</t>
+          <t>1015136</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1022542</t>
+          <t>1022541</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>12534</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29016</t>
+          <t>29068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13475</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30073</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>312264</t>
+          <t>312617</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>301033</t>
+          <t>301748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>318448</t>
+          <t>318582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>618063</t>
+          <t>617619</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>635278</t>
+          <t>635242</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14662</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15231</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>361314</t>
+          <t>361209</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>369124</t>
+          <t>368985</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>381595</t>
+          <t>381575</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>735315</t>
+          <t>734465</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>747888</t>
+          <t>748335</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>880</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7523</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>11111</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>203698</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>210327</t>
+          <t>210341</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11477,7 +11477,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>210941</t>
+          <t>210964</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>216934</t>
+          <t>217760</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>417093</t>
+          <t>417870</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>427121</t>
+          <t>427163</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7802</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>893</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>255321</t>
+          <t>254520</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>262176</t>
+          <t>262172</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>264847</t>
+          <t>264275</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>271225</t>
+          <t>271210</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>523013</t>
+          <t>523835</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>533313</t>
+          <t>532526</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>920</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>928</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13486</t>
+          <t>14111</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26342</t>
+          <t>27013</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15323</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>34744</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>638770</t>
+          <t>638145</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>650074</t>
+          <t>650023</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>656736</t>
+          <t>655906</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>674705</t>
+          <t>674172</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1299412</t>
+          <t>1301220</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1321184</t>
+          <t>1321414</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -12609,7 +12609,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>18567</t>
+          <t>19312</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>20218</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>18656</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>34161</t>
+          <t>33654</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>61424</t>
+          <t>61138</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>43610</t>
+          <t>43453</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>72741</t>
+          <t>72788</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>757889</t>
+          <t>757782</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>771004</t>
+          <t>770942</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>751568</t>
+          <t>751801</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>781886</t>
+          <t>780800</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1515475</t>
+          <t>1515716</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1548175</t>
+          <t>1548514</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11805</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>29426</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12947</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20971</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>43054</t>
+          <t>40827</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>87907</t>
+          <t>86340</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>126287</t>
+          <t>126815</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>115839</t>
+          <t>115714</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>161425</t>
+          <t>162373</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3334937</t>
+          <t>3336730</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3357023</t>
+          <t>3357336</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3384644</t>
+          <t>3385728</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3426550</t>
+          <t>3426760</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6729097</t>
+          <t>6729561</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6776837</t>
+          <t>6778372</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
